--- a/public/templates/business_capability.xlsx
+++ b/public/templates/business_capability.xlsx
@@ -5,24 +5,21 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlEMaksimov\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlEMaksimov\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8250"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
+    <sheet name="Business Capabilities" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>code</t>
   </si>
@@ -33,52 +30,35 @@
     <t>description</t>
   </si>
   <si>
+    <t>parents</t>
+  </si>
+  <si>
+    <t>isDomain</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
     <t>owner</t>
-  </si>
-  <si>
-    <t>created_date</t>
-  </si>
-  <si>
-    <t>last_modified_date</t>
-  </si>
-  <si>
-    <t>deleted_date</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>parent_id</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t>link</t>
-  </si>
-  <si>
-    <t>is_domain</t>
-  </si>
-  <si>
-    <t>source</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -89,7 +69,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -97,28 +77,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -399,67 +363,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2.36328125" customWidth="1"/>
-    <col min="2" max="2" width="4.81640625" customWidth="1"/>
-    <col min="3" max="3" width="5.54296875" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1796875" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.54296875" customWidth="1"/>
-    <col min="12" max="12" width="3.81640625" customWidth="1"/>
-    <col min="13" max="13" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.36328125" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
